--- a/Dados da Coffee mais/Dados extras/ESTRUTURA SALARIAL.xlsx
+++ b/Dados da Coffee mais/Dados extras/ESTRUTURA SALARIAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cristiano/Projetos/Coffe Mais/Dados da Coffee mais/Dados extras/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A7889D3-32F0-8A4A-9EF7-3173C67DA10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12822D2-0DE3-8646-A566-67F3D09EAAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="280" yWindow="600" windowWidth="28240" windowHeight="16280" xr2:uid="{61A966B8-27DB-1346-A837-00FF9B24CDA4}"/>
+    <workbookView xWindow="280" yWindow="600" windowWidth="28240" windowHeight="16240" xr2:uid="{61A966B8-27DB-1346-A837-00FF9B24CDA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -202,7 +202,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,6 +215,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -408,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -445,6 +451,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -784,11 +805,11 @@
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -798,7 +819,7 @@
       <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="18" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="15" t="s">
@@ -821,7 +842,7 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="19" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -844,7 +865,7 @@
       <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="20" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="8" t="s">
@@ -867,7 +888,7 @@
       <c r="B5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="21" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="12" t="s">
@@ -882,6 +903,9 @@
       <c r="G5" s="13" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C6" s="22"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -890,7 +914,7 @@
       <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="19" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="4" t="s">
@@ -913,7 +937,7 @@
       <c r="B8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="21" t="s">
         <v>36</v>
       </c>
       <c r="D8" s="12" t="s">
@@ -928,6 +952,9 @@
       <c r="G8" s="13" t="s">
         <v>17</v>
       </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C9" s="22"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
@@ -936,7 +963,7 @@
       <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="19" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -959,7 +986,7 @@
       <c r="B11" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D11" s="12" t="s">
@@ -974,6 +1001,9 @@
       <c r="G11" s="13" t="s">
         <v>17</v>
       </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C12" s="22"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
@@ -982,7 +1012,7 @@
       <c r="B13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="19" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -1005,7 +1035,7 @@
       <c r="B14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="20" t="s">
         <v>28</v>
       </c>
       <c r="D14" s="8" t="s">
@@ -1028,7 +1058,7 @@
       <c r="B15" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="21" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="12" t="s">
